--- a/Templates/PMTDP_Upload_Template.xlsx
+++ b/Templates/PMTDP_Upload_Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\93020457\MnE\MnE2_Planning\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E1964728-F79F-4393-B4E9-370920466666}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B04FDCC3-EA84-40C7-B243-DBAA8C31340F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{89F84AC6-25C3-423F-9F97-655C3B70616B}"/>
+    <workbookView xWindow="2200" yWindow="2200" windowWidth="19200" windowHeight="11170" xr2:uid="{5CBB6632-46D1-47C3-B28C-8FF7549CB8CD}"/>
   </bookViews>
   <sheets>
     <sheet name="PMTDP" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="43">
   <si>
     <t>Priority Focus</t>
   </si>
@@ -101,25 +101,28 @@
     <t>Spatial Reference</t>
   </si>
   <si>
-    <t>Economic Growth and Transformation</t>
-  </si>
-  <si>
-    <t>Inclusive Economic Growth</t>
-  </si>
-  <si>
-    <t>DEDEAT</t>
-  </si>
-  <si>
-    <t>Sustainable and inclusive economic growth achieved by 2030</t>
-  </si>
-  <si>
-    <t>GDP growth rate</t>
-  </si>
-  <si>
-    <t>NDP 2030</t>
-  </si>
-  <si>
-    <t>DPWI; DHS</t>
+    <t>Priority 1: Economic Growth</t>
+  </si>
+  <si>
+    <t>Integration Programme A</t>
+  </si>
+  <si>
+    <t>Dept of Economic Development</t>
+  </si>
+  <si>
+    <t>Increased employment rate</t>
+  </si>
+  <si>
+    <t>% unemployed youth placed in jobs</t>
+  </si>
+  <si>
+    <t>Percentage</t>
+  </si>
+  <si>
+    <t>Dept of Labour</t>
+  </si>
+  <si>
+    <t>SETA; NYDA</t>
   </si>
   <si>
     <t>No</t>
@@ -128,106 +131,43 @@
     <t>Yes</t>
   </si>
   <si>
-    <t>Increased contribution of key sectors to provincial GDP</t>
-  </si>
-  <si>
-    <t>% increase in GDP contribution from manufacturing sector</t>
-  </si>
-  <si>
-    <t>Province-wide</t>
-  </si>
-  <si>
-    <t>Unemployment rate</t>
-  </si>
-  <si>
-    <t>SDG 8</t>
-  </si>
-  <si>
-    <t>DSD; DPW</t>
-  </si>
-  <si>
-    <t>Job creation through EPWP and CWP programmes</t>
-  </si>
-  <si>
-    <t>Number of EPWP job opportunities created</t>
-  </si>
-  <si>
-    <t>All districts</t>
-  </si>
-  <si>
-    <t>Social Cohesion and Human Capital</t>
-  </si>
-  <si>
-    <t>Quality Education and Skills Development</t>
-  </si>
-  <si>
-    <t>DoBE</t>
-  </si>
-  <si>
-    <t>Improved learning outcomes and skills for economic participation</t>
-  </si>
-  <si>
-    <t>Matric pass rate</t>
-  </si>
-  <si>
-    <t>PDP 2030</t>
-  </si>
-  <si>
-    <t>DSBD; DEDEAT</t>
-  </si>
-  <si>
-    <t>Teacher development and classroom support programme</t>
-  </si>
-  <si>
-    <t>% of schools with trained foundation phase teachers</t>
-  </si>
-  <si>
-    <t>OR Tambo District; Alfred Nzo District</t>
-  </si>
-  <si>
-    <t>TVET enrolment</t>
-  </si>
-  <si>
-    <t>Africa Agenda 2063</t>
-  </si>
-  <si>
-    <t>DHET</t>
-  </si>
-  <si>
-    <t>DoBE; DEDEAT</t>
-  </si>
-  <si>
-    <t>Expansion of TVET college capacity and artisan programmes</t>
-  </si>
-  <si>
-    <t>Number of artisan learners enrolled at TVET colleges</t>
-  </si>
-  <si>
-    <t>Buffalo City; East London IDZ</t>
-  </si>
-  <si>
-    <t>Capable and Developmental State</t>
-  </si>
-  <si>
-    <t>Good Governance and Public Administration</t>
-  </si>
-  <si>
-    <t>OTP</t>
-  </si>
-  <si>
-    <t>Efficient and accountable public service delivery achieved</t>
-  </si>
-  <si>
-    <t>Departments with clean audit opinion</t>
-  </si>
-  <si>
-    <t>COGTA; NT</t>
-  </si>
-  <si>
-    <t>Departmental audit readiness and compliance support</t>
-  </si>
-  <si>
-    <t>Number of departments achieving clean audit opinion</t>
+    <t>Youth Employment Accelerator</t>
+  </si>
+  <si>
+    <t>% youth placed through accelerator</t>
+  </si>
+  <si>
+    <t>Limpopo - All Districts</t>
+  </si>
+  <si>
+    <t>Priority 2: Education</t>
+  </si>
+  <si>
+    <t>Integration Programme B</t>
+  </si>
+  <si>
+    <t>Dept of Education</t>
+  </si>
+  <si>
+    <t>Improved Grade 12 pass rate</t>
+  </si>
+  <si>
+    <t>% learners passing Grade 12</t>
+  </si>
+  <si>
+    <t>Dept of Basic Education</t>
+  </si>
+  <si>
+    <t>SACE; NSFAS</t>
+  </si>
+  <si>
+    <t>Maths &amp; Science Support</t>
+  </si>
+  <si>
+    <t>% learners improving in Maths/Science</t>
+  </si>
+  <si>
+    <t>All Districts</t>
   </si>
 </sst>
 </file>
@@ -251,7 +191,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -260,13 +200,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF4E6B1F"/>
+        <fgColor rgb="FF171717"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2FAF0"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -283,14 +229,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="10" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="9" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="9" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -624,33 +571,24 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10D0CAE9-6A2C-4591-9CA0-B19DF4DDF3D0}">
-  <dimension ref="A1:T6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4D738C0-DEBD-4FB6-A72E-E13D242E4508}">
+  <dimension ref="A1:T3"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="31.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36.6328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.90625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="53.90625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="31.1796875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.36328125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.1796875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.6328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="21.90625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="20.1796875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.36328125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="49.36328125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="48.26953125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="15.1796875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.90625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="11.1796875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="19.453125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="31.36328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.6328125" customWidth="1"/>
+    <col min="2" max="3" width="28.6328125" customWidth="1"/>
+    <col min="4" max="5" width="40.6328125" customWidth="1"/>
+    <col min="6" max="8" width="18.6328125" customWidth="1"/>
+    <col min="9" max="9" width="16.6328125" customWidth="1"/>
+    <col min="10" max="11" width="32.6328125" customWidth="1"/>
+    <col min="12" max="13" width="14.6328125" customWidth="1"/>
+    <col min="14" max="15" width="36.6328125" customWidth="1"/>
+    <col min="16" max="18" width="16.6328125" customWidth="1"/>
+    <col min="19" max="19" width="18.6328125" customWidth="1"/>
+    <col min="20" max="20" width="28.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:20" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -713,310 +651,148 @@
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="2">
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="H2" s="2">
-        <v>5.3999999999999999E-2</v>
-      </c>
-      <c r="I2">
-        <v>50000000</v>
-      </c>
-      <c r="J2" t="s">
-        <v>22</v>
-      </c>
-      <c r="K2" t="s">
+      <c r="G2" s="3">
+        <v>0.32</v>
+      </c>
+      <c r="H2" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="I2" s="2">
+        <v>5000000</v>
+      </c>
+      <c r="J2" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="L2" t="s">
+      <c r="K2" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M2" t="s">
+      <c r="L2" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="N2" t="s">
+      <c r="M2" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="O2" t="s">
+      <c r="N2" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="P2" s="2">
-        <v>2.1000000000000001E-2</v>
-      </c>
-      <c r="Q2" s="2">
-        <v>5.3999999999999999E-2</v>
-      </c>
-      <c r="R2">
-        <v>10000000</v>
-      </c>
-      <c r="S2" s="2">
-        <v>3.5000000000000003E-2</v>
-      </c>
-      <c r="T2" t="s">
+      <c r="O2" s="2" t="s">
         <v>31</v>
       </c>
+      <c r="P2" s="3">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="Q2" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="R2" s="2">
+        <v>2500000</v>
+      </c>
+      <c r="S2" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>32</v>
+      </c>
     </row>
-    <row r="3" spans="1:20" s="4" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="G3" s="5">
-        <v>0.42099999999999999</v>
-      </c>
-      <c r="H3" s="6">
-        <v>0.25</v>
+        <v>0.78</v>
+      </c>
+      <c r="H3" s="5">
+        <v>0.9</v>
       </c>
       <c r="I3" s="4">
-        <v>50000000</v>
+        <v>12000000</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="O3" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="P3" s="4">
-        <v>15000</v>
-      </c>
-      <c r="Q3" s="4">
-        <v>50000</v>
+        <v>41</v>
+      </c>
+      <c r="P3" s="5">
+        <v>0.65</v>
+      </c>
+      <c r="Q3" s="5">
+        <v>0.85</v>
       </c>
       <c r="R3" s="4">
-        <v>25000000</v>
-      </c>
-      <c r="S3" s="4">
-        <v>18000</v>
+        <v>6000000</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0.75</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B4" t="s">
-        <v>39</v>
-      </c>
-      <c r="C4" t="s">
-        <v>40</v>
-      </c>
-      <c r="D4" t="s">
-        <v>41</v>
-      </c>
-      <c r="E4" t="s">
         <v>42</v>
-      </c>
-      <c r="F4" t="s">
-        <v>43</v>
-      </c>
-      <c r="G4" s="2">
-        <v>0.68200000000000005</v>
-      </c>
-      <c r="H4" s="3">
-        <v>0.85</v>
-      </c>
-      <c r="I4">
-        <v>35000000</v>
-      </c>
-      <c r="J4" t="s">
-        <v>40</v>
-      </c>
-      <c r="K4" t="s">
-        <v>44</v>
-      </c>
-      <c r="L4" t="s">
-        <v>27</v>
-      </c>
-      <c r="M4" t="s">
-        <v>28</v>
-      </c>
-      <c r="N4" t="s">
-        <v>45</v>
-      </c>
-      <c r="O4" t="s">
-        <v>46</v>
-      </c>
-      <c r="P4" s="3">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="Q4" s="3">
-        <v>0.9</v>
-      </c>
-      <c r="R4">
-        <v>8000000</v>
-      </c>
-      <c r="S4" s="3">
-        <v>0.7</v>
-      </c>
-      <c r="T4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="G5" s="4">
-        <v>12000</v>
-      </c>
-      <c r="H5" s="4">
-        <v>30000</v>
-      </c>
-      <c r="I5" s="4">
-        <v>20000000</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="L5" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="M5" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="N5" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="O5" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="P5" s="4">
-        <v>3200</v>
-      </c>
-      <c r="Q5" s="4">
-        <v>12000</v>
-      </c>
-      <c r="R5" s="4">
-        <v>6000000</v>
-      </c>
-      <c r="S5" s="4">
-        <v>5000</v>
-      </c>
-      <c r="T5" s="4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B6" t="s">
-        <v>56</v>
-      </c>
-      <c r="C6" t="s">
-        <v>57</v>
-      </c>
-      <c r="D6" t="s">
-        <v>58</v>
-      </c>
-      <c r="E6" t="s">
-        <v>59</v>
-      </c>
-      <c r="F6" t="s">
-        <v>43</v>
-      </c>
-      <c r="G6">
-        <v>3</v>
-      </c>
-      <c r="H6">
-        <v>13</v>
-      </c>
-      <c r="J6" t="s">
-        <v>57</v>
-      </c>
-      <c r="K6" t="s">
-        <v>60</v>
-      </c>
-      <c r="L6" t="s">
-        <v>28</v>
-      </c>
-      <c r="M6" t="s">
-        <v>27</v>
-      </c>
-      <c r="N6" t="s">
-        <v>61</v>
-      </c>
-      <c r="O6" t="s">
-        <v>62</v>
-      </c>
-      <c r="P6">
-        <v>3</v>
-      </c>
-      <c r="Q6">
-        <v>13</v>
-      </c>
-      <c r="S6">
-        <v>6</v>
-      </c>
-      <c r="T6" t="s">
-        <v>31</v>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="Enter Yes or No" sqref="L2:M999" xr:uid="{6966BBAB-4828-4BC6-AA1F-6B3740A345EA}">
+      <mc:AlternateContent xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+        <mc:Choice Requires="x12ac">
+          <x12ac:list>"Yes,No"</x12ac:list>
+        </mc:Choice>
+        <mc:Fallback>
+          <formula1>"Yes,No"</formula1>
+        </mc:Fallback>
+      </mc:AlternateContent>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{7e917aa7-2b88-4a35-a1ca-6ad6798353d7}" enabled="1" method="Standard" siteId="{4ddc0aab-0096-426e-bba8-24cbf0387770}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>
--- a/Templates/PMTDP_Upload_Template.xlsx
+++ b/Templates/PMTDP_Upload_Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\93020457\MnE\MnE2_Planning\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B04FDCC3-EA84-40C7-B243-DBAA8C31340F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C6F21505-7331-4EFF-9C55-0D9BC5838B55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2200" yWindow="2200" windowWidth="19200" windowHeight="11170" xr2:uid="{5CBB6632-46D1-47C3-B28C-8FF7549CB8CD}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{88219EA6-BE04-4103-B1C5-25F8163268CA}"/>
   </bookViews>
   <sheets>
     <sheet name="PMTDP" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="39">
+  <si>
+    <t>PMTDP Upload Template  |  Sheet must remain named 'PMTDP'  |  Is Cumulative / Is Percentage: enter Yes or No  |  Do not delete or rename columns  |  Delete this row before uploading</t>
+  </si>
   <si>
     <t>Priority Focus</t>
   </si>
@@ -65,15 +68,9 @@
     <t>Term Target Value</t>
   </si>
   <si>
-    <t>Annual Budget</t>
-  </si>
-  <si>
     <t>Implementing Institution</t>
   </si>
   <si>
-    <t>Supporting Institutions</t>
-  </si>
-  <si>
     <t>Is Cumulative</t>
   </si>
   <si>
@@ -95,9 +92,6 @@
     <t>Term Budget</t>
   </si>
   <si>
-    <t>Annual Target 2025/26</t>
-  </si>
-  <si>
     <t>Spatial Reference</t>
   </si>
   <si>
@@ -122,9 +116,6 @@
     <t>Dept of Labour</t>
   </si>
   <si>
-    <t>SETA; NYDA</t>
-  </si>
-  <si>
     <t>No</t>
   </si>
   <si>
@@ -156,9 +147,6 @@
   </si>
   <si>
     <t>Dept of Basic Education</t>
-  </si>
-  <si>
-    <t>SACE; NSFAS</t>
   </si>
   <si>
     <t>Maths &amp; Science Support</t>
@@ -174,10 +162,18 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FF808080"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -191,12 +187,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -229,15 +231,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="9" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="9" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="9" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -571,212 +575,198 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4D738C0-DEBD-4FB6-A72E-E13D242E4508}">
-  <dimension ref="A1:T3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{806B7D51-2933-4ED0-AB9D-52965612FB0E}">
+  <dimension ref="A1:Q4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="30.6328125" customWidth="1"/>
     <col min="2" max="3" width="28.6328125" customWidth="1"/>
     <col min="4" max="5" width="40.6328125" customWidth="1"/>
     <col min="6" max="8" width="18.6328125" customWidth="1"/>
-    <col min="9" max="9" width="16.6328125" customWidth="1"/>
-    <col min="10" max="11" width="32.6328125" customWidth="1"/>
-    <col min="12" max="13" width="14.6328125" customWidth="1"/>
-    <col min="14" max="15" width="36.6328125" customWidth="1"/>
-    <col min="16" max="18" width="16.6328125" customWidth="1"/>
-    <col min="19" max="19" width="18.6328125" customWidth="1"/>
-    <col min="20" max="20" width="28.6328125" customWidth="1"/>
+    <col min="9" max="9" width="32.6328125" customWidth="1"/>
+    <col min="10" max="11" width="14.6328125" customWidth="1"/>
+    <col min="12" max="13" width="36.6328125" customWidth="1"/>
+    <col min="14" max="16" width="16.6328125" customWidth="1"/>
+    <col min="17" max="17" width="28.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="36" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:17" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="B2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="C2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="D2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="E2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="F2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="G2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="H2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="I2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="J2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="K2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="L2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="M2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="N2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="O2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="P2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="Q2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A3" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="B3" s="4" t="s">
         <v>19</v>
       </c>
+      <c r="C3" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" s="5">
+        <v>0.32</v>
+      </c>
+      <c r="H3" s="5">
+        <v>0.2</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="M3" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="N3" s="5">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="O3" s="5">
+        <v>0.15</v>
+      </c>
+      <c r="P3" s="4">
+        <v>2500000</v>
+      </c>
+      <c r="Q3" s="4" t="s">
+        <v>29</v>
+      </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D2" s="2" t="s">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A4" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="F4" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F2" s="2" t="s">
+      <c r="G4" s="7">
+        <v>0.78</v>
+      </c>
+      <c r="H4" s="7">
+        <v>0.9</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="J4" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="3">
-        <v>0.32</v>
-      </c>
-      <c r="H2" s="3">
-        <v>0.2</v>
-      </c>
-      <c r="I2" s="2">
-        <v>5000000</v>
-      </c>
-      <c r="J2" s="2" t="s">
+      <c r="K4" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="K2" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="P2" s="3">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="Q2" s="3">
-        <v>0.15</v>
-      </c>
-      <c r="R2" s="2">
-        <v>2500000</v>
-      </c>
-      <c r="S2" s="3">
-        <v>0.25</v>
-      </c>
-      <c r="T2" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A3" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D3" s="4" t="s">
+      <c r="L4" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="M4" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="F3" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="G3" s="5">
-        <v>0.78</v>
-      </c>
-      <c r="H3" s="5">
-        <v>0.9</v>
-      </c>
-      <c r="I3" s="4">
-        <v>12000000</v>
-      </c>
-      <c r="J3" s="4" t="s">
+      <c r="N4" s="7">
+        <v>0.65</v>
+      </c>
+      <c r="O4" s="7">
+        <v>0.85</v>
+      </c>
+      <c r="P4" s="6">
+        <v>6000000</v>
+      </c>
+      <c r="Q4" s="6" t="s">
         <v>38</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="L3" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="M3" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="N3" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="O3" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="P3" s="5">
-        <v>0.65</v>
-      </c>
-      <c r="Q3" s="5">
-        <v>0.85</v>
-      </c>
-      <c r="R3" s="4">
-        <v>6000000</v>
-      </c>
-      <c r="S3" s="5">
-        <v>0.75</v>
-      </c>
-      <c r="T3" s="4" t="s">
-        <v>42</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="Enter Yes or No" sqref="L2:M999" xr:uid="{6966BBAB-4828-4BC6-AA1F-6B3740A345EA}">
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="Enter Yes or No" sqref="J3:J1000" xr:uid="{8B2580C1-A76E-4D22-AE1B-9BC615F703A9}">
+      <mc:AlternateContent xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+        <mc:Choice Requires="x12ac">
+          <x12ac:list>"Yes,No"</x12ac:list>
+        </mc:Choice>
+        <mc:Fallback>
+          <formula1>"Yes,No"</formula1>
+        </mc:Fallback>
+      </mc:AlternateContent>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="Enter Yes or No" sqref="K3:K1000" xr:uid="{5131160F-57E1-4075-8E6E-C7B4B9B5AB0C}">
       <mc:AlternateContent xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
         <mc:Choice Requires="x12ac">
           <x12ac:list>"Yes,No"</x12ac:list>

--- a/Templates/PMTDP_Upload_Template.xlsx
+++ b/Templates/PMTDP_Upload_Template.xlsx
@@ -1,56 +1,52 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\93020457\MnE\MnE2_Planning\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C6F21505-7331-4EFF-9C55-0D9BC5838B55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FC76E54-830F-498D-92EB-0306A1D26660}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{88219EA6-BE04-4103-B1C5-25F8163268CA}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PMTDP" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="2"/>
-    </ext>
-  </extLst>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">PMTDP!$A$7:$O$7</definedName>
+  </definedNames>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="39">
-  <si>
-    <t>PMTDP Upload Template  |  Sheet must remain named 'PMTDP'  |  Is Cumulative / Is Percentage: enter Yes or No  |  Do not delete or rename columns  |  Delete this row before uploading</t>
-  </si>
-  <si>
-    <t>Priority Focus</t>
-  </si>
-  <si>
-    <t>Integration Programme</t>
-  </si>
-  <si>
-    <t>Leading Department</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="44">
+  <si>
+    <t>PMTDP Upload Template  |  Fill in Rows 2-5 first, then add one intervention-indicator per row from Row 7 onwards  |  Do NOT rename this sheet or change column headers</t>
+  </si>
+  <si>
+    <t>Provincial Development Plan Goal</t>
+  </si>
+  <si>
+    <t>[Enter the PDP Goal e.g. Innovative and inclusive growing economy]</t>
+  </si>
+  <si>
+    <t>Priority Focus:</t>
+  </si>
+  <si>
+    <t>[Enter Priority Focus e.g. Priority 1: Economic Transformation]</t>
+  </si>
+  <si>
+    <t>Integration Programme:</t>
+  </si>
+  <si>
+    <t>Impact:</t>
+  </si>
+  <si>
+    <t>[Enter the overall Impact Statement for this programme]</t>
   </si>
   <si>
     <t>Desired Outcome</t>
@@ -62,22 +58,25 @@
     <t>Indicator Type</t>
   </si>
   <si>
-    <t>Baseline Value</t>
-  </si>
-  <si>
-    <t>Term Target Value</t>
+    <t>PDP Baseline 2019/2020</t>
+  </si>
+  <si>
+    <t>PDP Target 2030</t>
   </si>
   <si>
     <t>Implementing Institution</t>
   </si>
   <si>
+    <t>Supporting Institutions</t>
+  </si>
+  <si>
     <t>Is Cumulative</t>
   </si>
   <si>
     <t>Is Percentage</t>
   </si>
   <si>
-    <t>Intervention Name</t>
+    <t>Intervention</t>
   </si>
   <si>
     <t>Intervention Indicator</t>
@@ -86,34 +85,34 @@
     <t>Baseline 2023/24</t>
   </si>
   <si>
-    <t>Term Target 2030</t>
+    <t>Term Target 2025-2030</t>
   </si>
   <si>
     <t>Term Budget</t>
   </si>
   <si>
-    <t>Spatial Reference</t>
-  </si>
-  <si>
-    <t>Priority 1: Economic Growth</t>
-  </si>
-  <si>
-    <t>Integration Programme A</t>
-  </si>
-  <si>
-    <t>Dept of Economic Development</t>
-  </si>
-  <si>
-    <t>Increased employment rate</t>
-  </si>
-  <si>
-    <t>% unemployed youth placed in jobs</t>
-  </si>
-  <si>
-    <t>Percentage</t>
-  </si>
-  <si>
-    <t>Dept of Labour</t>
+    <t>Spatial Referencing</t>
+  </si>
+  <si>
+    <t>Innovation and inclusive growing economy</t>
+  </si>
+  <si>
+    <t>GDP growth rate</t>
+  </si>
+  <si>
+    <t>PDP 2030</t>
+  </si>
+  <si>
+    <t>1.5% (2020)</t>
+  </si>
+  <si>
+    <t>5.4%</t>
+  </si>
+  <si>
+    <t>ECDC</t>
+  </si>
+  <si>
+    <t>DEDEAT</t>
   </si>
   <si>
     <t>No</t>
@@ -122,72 +121,75 @@
     <t>Yes</t>
   </si>
   <si>
-    <t>Youth Employment Accelerator</t>
-  </si>
-  <si>
-    <t>% youth placed through accelerator</t>
-  </si>
-  <si>
-    <t>Limpopo - All Districts</t>
-  </si>
-  <si>
-    <t>Priority 2: Education</t>
-  </si>
-  <si>
-    <t>Integration Programme B</t>
-  </si>
-  <si>
-    <t>Dept of Education</t>
-  </si>
-  <si>
-    <t>Improved Grade 12 pass rate</t>
-  </si>
-  <si>
-    <t>% learners passing Grade 12</t>
-  </si>
-  <si>
-    <t>Dept of Basic Education</t>
-  </si>
-  <si>
-    <t>Maths &amp; Science Support</t>
-  </si>
-  <si>
-    <t>% learners improving in Maths/Science</t>
-  </si>
-  <si>
-    <t>All Districts</t>
+    <t>Ensure a growing, innovative and diversified SMME led economy</t>
+  </si>
+  <si>
+    <t>Number of cooperatives provided with financial support</t>
+  </si>
+  <si>
+    <t>55</t>
+  </si>
+  <si>
+    <t>350</t>
+  </si>
+  <si>
+    <t>Awaiting final budget</t>
+  </si>
+  <si>
+    <t>EC Province</t>
+  </si>
+  <si>
+    <t>ECRDA</t>
+  </si>
+  <si>
+    <t>Number of cooperatives provided with non-financial support</t>
+  </si>
+  <si>
+    <t>640</t>
+  </si>
+  <si>
+    <t>1000</t>
+  </si>
+  <si>
+    <t>Operational budget</t>
+  </si>
+  <si>
+    <t>[Enter the Integration Programme name]</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
-      <color theme="1"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF92400E"/>
+      <name val="Aptos Narrow"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Aptos Narrow"/>
     </font>
     <font>
       <i/>
-      <sz val="9"/>
-      <color rgb="FF808080"/>
+      <sz val="10"/>
+      <color rgb="FF8B9AB4"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -196,30 +198,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCCFFFF"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FFFFFBEB"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF171717"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FF1A3E60"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FFF0F4F8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FF0C2D48"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFF4FB"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -227,21 +230,48 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFDCE3EC"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFDCE3EC"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFDCE3EC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFDCE3EC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="9" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="9" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -575,208 +605,622 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{806B7D51-2933-4ED0-AB9D-52965612FB0E}">
-  <dimension ref="A1:Q4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr>
+    <tabColor rgb="FF0C2D48"/>
+  </sheetPr>
+  <dimension ref="A1:O29"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="30.6328125" customWidth="1"/>
-    <col min="2" max="3" width="28.6328125" customWidth="1"/>
-    <col min="4" max="5" width="40.6328125" customWidth="1"/>
-    <col min="6" max="8" width="18.6328125" customWidth="1"/>
-    <col min="9" max="9" width="32.6328125" customWidth="1"/>
-    <col min="10" max="11" width="14.6328125" customWidth="1"/>
-    <col min="12" max="13" width="36.6328125" customWidth="1"/>
-    <col min="14" max="16" width="16.6328125" customWidth="1"/>
-    <col min="17" max="17" width="28.6328125" customWidth="1"/>
+    <col min="1" max="1" width="30" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="18" customWidth="1"/>
+    <col min="5" max="5" width="14" customWidth="1"/>
+    <col min="6" max="7" width="24" customWidth="1"/>
+    <col min="8" max="9" width="13" customWidth="1"/>
+    <col min="10" max="10" width="34" customWidth="1"/>
+    <col min="11" max="11" width="36" customWidth="1"/>
+    <col min="12" max="12" width="15" customWidth="1"/>
+    <col min="13" max="13" width="18" customWidth="1"/>
+    <col min="14" max="14" width="20" customWidth="1"/>
+    <col min="15" max="15" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:15" ht="24" customHeight="1">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:17" ht="36" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="3" t="s">
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="8"/>
+      <c r="M1" s="8"/>
+      <c r="N1" s="8"/>
+      <c r="O1" s="8"/>
+    </row>
+    <row r="2" spans="1:15" ht="22" customHeight="1">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="8"/>
+      <c r="I2" s="8"/>
+      <c r="J2" s="8"/>
+      <c r="K2" s="8"/>
+      <c r="L2" s="8"/>
+      <c r="M2" s="8"/>
+      <c r="N2" s="8"/>
+      <c r="O2" s="8"/>
+    </row>
+    <row r="3" spans="1:15" ht="22" customHeight="1">
+      <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="B3" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="8"/>
+      <c r="I3" s="8"/>
+      <c r="J3" s="8"/>
+      <c r="K3" s="8"/>
+      <c r="L3" s="8"/>
+      <c r="M3" s="8"/>
+      <c r="N3" s="8"/>
+      <c r="O3" s="8"/>
+    </row>
+    <row r="4" spans="1:15" ht="22" customHeight="1">
+      <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="B4" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="8"/>
+      <c r="K4" s="8"/>
+      <c r="L4" s="8"/>
+      <c r="M4" s="8"/>
+      <c r="N4" s="8"/>
+      <c r="O4" s="8"/>
+    </row>
+    <row r="5" spans="1:15" ht="22" customHeight="1">
+      <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="B5" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="8"/>
+      <c r="K5" s="8"/>
+      <c r="L5" s="8"/>
+      <c r="M5" s="8"/>
+      <c r="N5" s="8"/>
+      <c r="O5" s="8"/>
+    </row>
+    <row r="6" spans="1:15" ht="6" customHeight="1"/>
+    <row r="7" spans="1:15" ht="36" customHeight="1">
+      <c r="A7" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="B7" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="C7" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="D7" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="E7" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="M2" s="3" t="s">
+      <c r="F7" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="N2" s="3" t="s">
+      <c r="G7" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="O2" s="3" t="s">
+      <c r="H7" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="P2" s="3" t="s">
+      <c r="I7" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="Q2" s="3" t="s">
+      <c r="J7" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A3" s="4" t="s">
+      <c r="K7" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="L7" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="M7" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="N7" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="O7" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="F3" s="4" t="s">
+    </row>
+    <row r="8" spans="1:15" ht="36" customHeight="1">
+      <c r="A8" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="5">
-        <v>0.32</v>
-      </c>
-      <c r="H3" s="5">
-        <v>0.2</v>
-      </c>
-      <c r="I3" s="4" t="s">
+      <c r="B8" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="C8" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="D8" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="L3" s="4" t="s">
+      <c r="E8" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="M3" s="4" t="s">
+      <c r="F8" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="N3" s="5">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="O3" s="5">
-        <v>0.15</v>
-      </c>
-      <c r="P3" s="4">
-        <v>2500000</v>
-      </c>
-      <c r="Q3" s="4" t="s">
+      <c r="G8" s="3" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A4" s="6" t="s">
+      <c r="H8" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="I8" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="J8" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="K8" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="L8" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="M8" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" ht="36" customHeight="1">
+      <c r="A9" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="G4" s="7">
-        <v>0.78</v>
-      </c>
-      <c r="H4" s="7">
-        <v>0.9</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="J4" s="6" t="s">
+      <c r="B9" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="K4" s="6" t="s">
+      <c r="D9" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="L4" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="M4" s="6" t="s">
+      <c r="E9" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="L9" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="M9" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="N9" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="O9" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="N4" s="7">
-        <v>0.65</v>
-      </c>
-      <c r="O4" s="7">
-        <v>0.85</v>
-      </c>
-      <c r="P4" s="6">
-        <v>6000000</v>
-      </c>
-      <c r="Q4" s="6" t="s">
-        <v>38</v>
-      </c>
+    </row>
+    <row r="10" spans="1:15" ht="20" customHeight="1">
+      <c r="A10" s="5"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
+      <c r="J10" s="5"/>
+      <c r="K10" s="5"/>
+      <c r="L10" s="5"/>
+      <c r="M10" s="5"/>
+      <c r="N10" s="5"/>
+      <c r="O10" s="5"/>
+    </row>
+    <row r="11" spans="1:15" ht="20" customHeight="1">
+      <c r="A11" s="6"/>
+      <c r="B11" s="6"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6"/>
+      <c r="I11" s="6"/>
+      <c r="J11" s="6"/>
+      <c r="K11" s="6"/>
+      <c r="L11" s="6"/>
+      <c r="M11" s="6"/>
+      <c r="N11" s="6"/>
+      <c r="O11" s="6"/>
+    </row>
+    <row r="12" spans="1:15" ht="20" customHeight="1">
+      <c r="A12" s="5"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="5"/>
+      <c r="K12" s="5"/>
+      <c r="L12" s="5"/>
+      <c r="M12" s="5"/>
+      <c r="N12" s="5"/>
+      <c r="O12" s="5"/>
+    </row>
+    <row r="13" spans="1:15" ht="20" customHeight="1">
+      <c r="A13" s="6"/>
+      <c r="B13" s="6"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="6"/>
+      <c r="I13" s="6"/>
+      <c r="J13" s="6"/>
+      <c r="K13" s="6"/>
+      <c r="L13" s="6"/>
+      <c r="M13" s="6"/>
+      <c r="N13" s="6"/>
+      <c r="O13" s="6"/>
+    </row>
+    <row r="14" spans="1:15" ht="20" customHeight="1">
+      <c r="A14" s="5"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5"/>
+      <c r="K14" s="5"/>
+      <c r="L14" s="5"/>
+      <c r="M14" s="5"/>
+      <c r="N14" s="5"/>
+      <c r="O14" s="5"/>
+    </row>
+    <row r="15" spans="1:15" ht="20" customHeight="1">
+      <c r="A15" s="6"/>
+      <c r="B15" s="6"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="6"/>
+      <c r="H15" s="6"/>
+      <c r="I15" s="6"/>
+      <c r="J15" s="6"/>
+      <c r="K15" s="6"/>
+      <c r="L15" s="6"/>
+      <c r="M15" s="6"/>
+      <c r="N15" s="6"/>
+      <c r="O15" s="6"/>
+    </row>
+    <row r="16" spans="1:15" ht="20" customHeight="1">
+      <c r="A16" s="5"/>
+      <c r="B16" s="5"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5"/>
+      <c r="K16" s="5"/>
+      <c r="L16" s="5"/>
+      <c r="M16" s="5"/>
+      <c r="N16" s="5"/>
+      <c r="O16" s="5"/>
+    </row>
+    <row r="17" spans="1:15" ht="20" customHeight="1">
+      <c r="A17" s="6"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="6"/>
+      <c r="I17" s="6"/>
+      <c r="J17" s="6"/>
+      <c r="K17" s="6"/>
+      <c r="L17" s="6"/>
+      <c r="M17" s="6"/>
+      <c r="N17" s="6"/>
+      <c r="O17" s="6"/>
+    </row>
+    <row r="18" spans="1:15" ht="20" customHeight="1">
+      <c r="A18" s="5"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="5"/>
+      <c r="K18" s="5"/>
+      <c r="L18" s="5"/>
+      <c r="M18" s="5"/>
+      <c r="N18" s="5"/>
+      <c r="O18" s="5"/>
+    </row>
+    <row r="19" spans="1:15" ht="20" customHeight="1">
+      <c r="A19" s="6"/>
+      <c r="B19" s="6"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="6"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="6"/>
+      <c r="G19" s="6"/>
+      <c r="H19" s="6"/>
+      <c r="I19" s="6"/>
+      <c r="J19" s="6"/>
+      <c r="K19" s="6"/>
+      <c r="L19" s="6"/>
+      <c r="M19" s="6"/>
+      <c r="N19" s="6"/>
+      <c r="O19" s="6"/>
+    </row>
+    <row r="20" spans="1:15" ht="20" customHeight="1">
+      <c r="A20" s="5"/>
+      <c r="B20" s="5"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
+      <c r="J20" s="5"/>
+      <c r="K20" s="5"/>
+      <c r="L20" s="5"/>
+      <c r="M20" s="5"/>
+      <c r="N20" s="5"/>
+      <c r="O20" s="5"/>
+    </row>
+    <row r="21" spans="1:15" ht="20" customHeight="1">
+      <c r="A21" s="6"/>
+      <c r="B21" s="6"/>
+      <c r="C21" s="6"/>
+      <c r="D21" s="6"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="6"/>
+      <c r="G21" s="6"/>
+      <c r="H21" s="6"/>
+      <c r="I21" s="6"/>
+      <c r="J21" s="6"/>
+      <c r="K21" s="6"/>
+      <c r="L21" s="6"/>
+      <c r="M21" s="6"/>
+      <c r="N21" s="6"/>
+      <c r="O21" s="6"/>
+    </row>
+    <row r="22" spans="1:15" ht="20" customHeight="1">
+      <c r="A22" s="5"/>
+      <c r="B22" s="5"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5"/>
+      <c r="J22" s="5"/>
+      <c r="K22" s="5"/>
+      <c r="L22" s="5"/>
+      <c r="M22" s="5"/>
+      <c r="N22" s="5"/>
+      <c r="O22" s="5"/>
+    </row>
+    <row r="23" spans="1:15" ht="20" customHeight="1">
+      <c r="A23" s="6"/>
+      <c r="B23" s="6"/>
+      <c r="C23" s="6"/>
+      <c r="D23" s="6"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="6"/>
+      <c r="G23" s="6"/>
+      <c r="H23" s="6"/>
+      <c r="I23" s="6"/>
+      <c r="J23" s="6"/>
+      <c r="K23" s="6"/>
+      <c r="L23" s="6"/>
+      <c r="M23" s="6"/>
+      <c r="N23" s="6"/>
+      <c r="O23" s="6"/>
+    </row>
+    <row r="24" spans="1:15" ht="20" customHeight="1">
+      <c r="A24" s="5"/>
+      <c r="B24" s="5"/>
+      <c r="C24" s="5"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5"/>
+      <c r="G24" s="5"/>
+      <c r="H24" s="5"/>
+      <c r="I24" s="5"/>
+      <c r="J24" s="5"/>
+      <c r="K24" s="5"/>
+      <c r="L24" s="5"/>
+      <c r="M24" s="5"/>
+      <c r="N24" s="5"/>
+      <c r="O24" s="5"/>
+    </row>
+    <row r="25" spans="1:15" ht="20" customHeight="1">
+      <c r="A25" s="6"/>
+      <c r="B25" s="6"/>
+      <c r="C25" s="6"/>
+      <c r="D25" s="6"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="6"/>
+      <c r="G25" s="6"/>
+      <c r="H25" s="6"/>
+      <c r="I25" s="6"/>
+      <c r="J25" s="6"/>
+      <c r="K25" s="6"/>
+      <c r="L25" s="6"/>
+      <c r="M25" s="6"/>
+      <c r="N25" s="6"/>
+      <c r="O25" s="6"/>
+    </row>
+    <row r="26" spans="1:15" ht="20" customHeight="1">
+      <c r="A26" s="5"/>
+      <c r="B26" s="5"/>
+      <c r="C26" s="5"/>
+      <c r="D26" s="5"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="5"/>
+      <c r="G26" s="5"/>
+      <c r="H26" s="5"/>
+      <c r="I26" s="5"/>
+      <c r="J26" s="5"/>
+      <c r="K26" s="5"/>
+      <c r="L26" s="5"/>
+      <c r="M26" s="5"/>
+      <c r="N26" s="5"/>
+      <c r="O26" s="5"/>
+    </row>
+    <row r="27" spans="1:15" ht="20" customHeight="1">
+      <c r="A27" s="6"/>
+      <c r="B27" s="6"/>
+      <c r="C27" s="6"/>
+      <c r="D27" s="6"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="6"/>
+      <c r="G27" s="6"/>
+      <c r="H27" s="6"/>
+      <c r="I27" s="6"/>
+      <c r="J27" s="6"/>
+      <c r="K27" s="6"/>
+      <c r="L27" s="6"/>
+      <c r="M27" s="6"/>
+      <c r="N27" s="6"/>
+      <c r="O27" s="6"/>
+    </row>
+    <row r="28" spans="1:15" ht="20" customHeight="1">
+      <c r="A28" s="5"/>
+      <c r="B28" s="5"/>
+      <c r="C28" s="5"/>
+      <c r="D28" s="5"/>
+      <c r="E28" s="5"/>
+      <c r="F28" s="5"/>
+      <c r="G28" s="5"/>
+      <c r="H28" s="5"/>
+      <c r="I28" s="5"/>
+      <c r="J28" s="5"/>
+      <c r="K28" s="5"/>
+      <c r="L28" s="5"/>
+      <c r="M28" s="5"/>
+      <c r="N28" s="5"/>
+      <c r="O28" s="5"/>
+    </row>
+    <row r="29" spans="1:15" ht="20" customHeight="1">
+      <c r="A29" s="6"/>
+      <c r="B29" s="6"/>
+      <c r="C29" s="6"/>
+      <c r="D29" s="6"/>
+      <c r="E29" s="6"/>
+      <c r="F29" s="6"/>
+      <c r="G29" s="6"/>
+      <c r="H29" s="6"/>
+      <c r="I29" s="6"/>
+      <c r="J29" s="6"/>
+      <c r="K29" s="6"/>
+      <c r="L29" s="6"/>
+      <c r="M29" s="6"/>
+      <c r="N29" s="6"/>
+      <c r="O29" s="6"/>
     </row>
   </sheetData>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="Enter Yes or No" sqref="J3:J1000" xr:uid="{8B2580C1-A76E-4D22-AE1B-9BC615F703A9}">
-      <mc:AlternateContent xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-        <mc:Choice Requires="x12ac">
-          <x12ac:list>"Yes,No"</x12ac:list>
-        </mc:Choice>
-        <mc:Fallback>
-          <formula1>"Yes,No"</formula1>
-        </mc:Fallback>
-      </mc:AlternateContent>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="Enter Yes or No" sqref="K3:K1000" xr:uid="{5131160F-57E1-4075-8E6E-C7B4B9B5AB0C}">
-      <mc:AlternateContent xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-        <mc:Choice Requires="x12ac">
-          <x12ac:list>"Yes,No"</x12ac:list>
-        </mc:Choice>
-        <mc:Fallback>
-          <formula1>"Yes,No"</formula1>
-        </mc:Fallback>
-      </mc:AlternateContent>
-    </dataValidation>
-  </dataValidations>
+  <autoFilter ref="A7:O7" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <mergeCells count="5">
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="B2:O2"/>
+    <mergeCell ref="B3:O3"/>
+    <mergeCell ref="B4:O4"/>
+    <mergeCell ref="B5:O5"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/Templates/PMTDP_Upload_Template.xlsx
+++ b/Templates/PMTDP_Upload_Template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\93020457\MnE\MnE2_Planning\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FC76E54-830F-498D-92EB-0306A1D26660}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{637A6841-0C7D-4B4A-8C16-A671E12A43E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,6 +19,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">PMTDP!$A$7:$O$7</definedName>
   </definedNames>
   <calcPr calcId="0"/>
+  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
@@ -31,24 +32,15 @@
     <t>Provincial Development Plan Goal</t>
   </si>
   <si>
-    <t>[Enter the PDP Goal e.g. Innovative and inclusive growing economy]</t>
-  </si>
-  <si>
     <t>Priority Focus:</t>
   </si>
   <si>
-    <t>[Enter Priority Focus e.g. Priority 1: Economic Transformation]</t>
-  </si>
-  <si>
     <t>Integration Programme:</t>
   </si>
   <si>
     <t>Impact:</t>
   </si>
   <si>
-    <t>[Enter the overall Impact Statement for this programme]</t>
-  </si>
-  <si>
     <t>Desired Outcome</t>
   </si>
   <si>
@@ -154,7 +146,16 @@
     <t>Operational budget</t>
   </si>
   <si>
-    <t>[Enter the Integration Programme name]</t>
+    <t>Innovative and inclusive growing economy</t>
+  </si>
+  <si>
+    <t>Economic Growth</t>
+  </si>
+  <si>
+    <t>Inclusive Economic Growth</t>
+  </si>
+  <si>
+    <t>Sustainable and inclusive economic growth</t>
   </si>
 </sst>
 </file>
@@ -651,7 +652,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="C2" s="8"/>
       <c r="D2" s="8"/>
@@ -669,10 +670,10 @@
     </row>
     <row r="3" spans="1:15" ht="22" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="C3" s="8"/>
       <c r="D3" s="8"/>
@@ -690,10 +691,10 @@
     </row>
     <row r="4" spans="1:15" ht="22" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -711,10 +712,10 @@
     </row>
     <row r="5" spans="1:15" ht="22" customHeight="1">
       <c r="A5" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>7</v>
+        <v>43</v>
       </c>
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
@@ -733,143 +734,143 @@
     <row r="6" spans="1:15" ht="6" customHeight="1"/>
     <row r="7" spans="1:15" ht="36" customHeight="1">
       <c r="A7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="G7" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="H7" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="I7" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="J7" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="K7" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="I7" s="2" t="s">
+      <c r="L7" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="J7" s="2" t="s">
+      <c r="M7" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="K7" s="2" t="s">
+      <c r="N7" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="L7" s="2" t="s">
+      <c r="O7" s="2" t="s">
         <v>19</v>
-      </c>
-      <c r="M7" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="N7" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="O7" s="2" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:15" ht="36" customHeight="1">
       <c r="A8" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="E8" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="F8" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="G8" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="H8" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="I8" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="J8" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="H8" s="3" t="s">
+      <c r="K8" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="I8" s="3" t="s">
+      <c r="L8" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="J8" s="3" t="s">
+      <c r="M8" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="K8" s="3" t="s">
+      <c r="N8" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="L8" s="3" t="s">
+      <c r="O8" s="3" t="s">
         <v>34</v>
-      </c>
-      <c r="M8" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="N8" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="O8" s="3" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:15" ht="36" customHeight="1">
       <c r="A9" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="E9" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C9" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D9" s="4" t="s">
+      <c r="F9" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G9" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="H9" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="I9" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="L9" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="M9" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="G9" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="I9" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="J9" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="K9" s="4" t="s">
+      <c r="N9" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="L9" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="M9" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="N9" s="4" t="s">
-        <v>42</v>
-      </c>
       <c r="O9" s="4" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" spans="1:15" ht="20" customHeight="1">
